--- a/Result/checksun_type/太陽能電池.xlsx
+++ b/Result/checksun_type/太陽能電池.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>12.39</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>13.29</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>14.15</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>14.15</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>26119704.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>34501382.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>34501382</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>34609485.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>42902057.1</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>42902057.1</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-577637.104703553</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>26119704</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>26119704.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>12.45</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>13.39</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>14.18</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>14.18</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>35214902.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>40716516.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>40716516.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>34123731.5</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>43308539.52</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>43308539.52</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>203672.4769979939</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>35214902</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>35214902.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>12.63</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>14.22</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>14.22</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>43737691.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>41001956.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>41001956.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>32899981.8</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>43494788.36</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>43494788.36</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>338069.5052502751</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>43737691</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>43737691.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>12.93</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>13.62</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>14.27</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>14.27</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>33272234.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>36292512.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>36292512.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>30682542.9</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>43382880.32</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>43382880.32</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-395164.6152911186</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>33272234</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>33272234.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>13.14</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>13.7</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>14.32</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>14.32</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>34162379.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>34419396.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>34419396.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>28993242.5</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>43440651.04</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>43440651.04</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-307229.9440898597</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>34162379</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>34162379.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>13.26</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>13.78</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>14.36</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>14.36</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>57195376.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>34717588.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>34717588.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>28221070.3</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>43323447.32</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>43323447.32</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-266009.1657991186</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>57195376</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>57195376.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>13.41</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>13.85</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>14.4</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>14.4</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>36642104.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>27530946.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>27530946.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>25536290.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>42917345.92</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>42917345.92</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-2665443.119462393</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>36642104</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>36642104.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>13.45</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>13.89</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>14.43</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>14.43</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>20190471.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>24798006.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>24798006.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>26300943.2</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>42871371.14</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>42871371.14</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-3795875.227571983</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>20190471</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>20190471.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>13.44</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>13.92</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>14.45</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>23906651.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>25072573.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>25072573</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>29070275.6</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>43769603.24</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>43769603.24</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-3512536.302458107</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>23906651</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>23906651.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>13.51</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>13.97</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>14.49</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>14.49</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>35653342.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>23567088.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>23567088.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>31620576.3</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>44172918.42</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>44172918.42</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-3380480.82720764</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>35653342</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>35653342.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>13.63</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>14.01</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>14.53</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>14.53</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>21262165.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>21724551.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>21724551.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>37530399.8</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>45039926.82</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>45039926.82</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-4329672.725878127</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>21262165</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>21262165.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>15.42</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>16.18</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>16.83</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>16.83</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>14634.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>14548.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>14548.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>17818.7</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>29999.06</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>29999.06</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-2902.427356930613</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>14634</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>14634.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>15.37</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>16.84</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>16.84</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>12839.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>17159.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>17159</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>17915.0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>30233.9</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>30233.9</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-3020.99928076757</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>12839</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>12839.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>15.43</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>16.37</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>16.87</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>16.87</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>10453.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>21846.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>21846.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>17928.2</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>30585.48</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>30585.48</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-2890.173483364375</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>10453</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>10453.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>15.66</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>16.48</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>16.92</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>16.92</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>16476.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>23074.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>23074.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>18946.2</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>30922.64</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>30922.64</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-2344.416148382516</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>16476</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>16476.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>15.9</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>16.58</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>16.96</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>16.96</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>18342.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>21525.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>21525.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>19455.3</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>30997.64</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>30997.64</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-2126.355093109058</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>18342</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>18342.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>16.08</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>16.65</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>16.99</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>16.99</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>27685.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>21088.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>21088.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>19477.0</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>31133.42</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>31133.42</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-1938.826617964503</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>27685</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>27685.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>16.29</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>16.74</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>17.03</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>17.03</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>36278.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>18671.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>18671</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>19526.2</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>31199.22</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>31199.22</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-2602.720702830695</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>36278</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>36278.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>16.39</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>16.8</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>17.05</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>17.05</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>16590.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>14009.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>14009.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>18938.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>31611.14</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>31611.14</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-4378.8650846813</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>16590</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>16590.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>16.37</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>16.82</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>17.07</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>17.07</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>8734.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>14818.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>14818.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>20712.1</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>32177.64</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>32177.64</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-4650.397591443547</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>8734</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>8734.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>16.33</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>16.85</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>17.09</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>17.09</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>16156.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>17384.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>17384.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>23754.9</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>32606.84</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>32606.84</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-4030.501258552344</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>16156</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>16156.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>16.35</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>16.86</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>17.12</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>17.12</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>15597.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>17865.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>17865.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>34457.9</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>32784.24</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>32784.24</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-3796.202880902329</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>15597</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>15597.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>100.96</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>108.88</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>116.13</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>108.88</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>116.13</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>507293.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>390648.2</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>390648.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>413482.5</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>1173198.42</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>1173198.42</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-65273.64825404435</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>507293</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>507293.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>100.06</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>110.12</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>116.12</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>110.12</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>116.12</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>370028.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>379489.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>379489.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>396910.1</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>1169863.72</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>1169863.72</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-81758.93193293636</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>370028</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>370028.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>99.2</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>111.22</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>116.13</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>111.22</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>116.13</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>304877.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>414526.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>414526.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>426922.8</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>1168955.64</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>1168955.64</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-87682.41104803438</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>304877</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>304877.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>99.3</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>112.68</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>116.22</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>112.68</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>116.22</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>383570.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>425777.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>425777</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>497277.9</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>1168885.06</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>1168885.06</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-86032.54510360176</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>383570</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>383570.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>100.24</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>114.31</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>116.34</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>114.31</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>116.34</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>387473.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>423142.2</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>423142.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>499779.7</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>1165775.88</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>1165775.88</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-89034.3957149979</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>387473</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>387473.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>101.14</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>115.74</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>116.41</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>115.74</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>116.41</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>451500.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>436316.8</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>436316.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>531910.4</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>1161801.62</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>1161801.62</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-90561.13245574245</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>451500</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>451500.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>102.74</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>117.36</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>116.56</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>117.36</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>116.56</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>545212.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>414330.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>414330.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>573471.0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>1159595.78</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>1159595.78</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-96367.89449767256</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>545212</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>545212.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>103.9</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>118.62</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>116.62</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>118.62</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>116.62</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>361130.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>439319.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>439319.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>585928.9</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>1153377.78</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>1153377.78</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-111262.1297540844</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>361130</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>361130.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>105.0</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>119.62</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>116.59</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>119.62</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>116.59</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>370396.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>568778.8</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>568778.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>603621.1</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>1153337.92</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>1153337.92</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-108842.8897720267</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>370396</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>370396.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>107.4</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>120.78</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>116.56</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>120.78</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>116.56</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>453346.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>576417.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>576417.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>601468.9</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>1151585.72</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>1151585.72</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-102492.3723058006</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>453346</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>453346.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>109.9</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>121.72</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>116.54</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>116.54</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>341569.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>627504.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>627504</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>615295.8</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>1146810.3</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>1146810.3</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-98647.2626288418</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>341569</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>341569.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>12.04</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>13.29</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>14.27</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>14.27</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>4596524.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>6136300.4</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>6136300.4</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>7073001.0</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>30854093.86</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>30854093.86</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-2169313.085164293</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>4596524</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>4596524.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>12.04</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>13.43</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>14.23</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>14.23</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>6558890.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>6146868.2</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>6146868.2</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>7224979.7</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>30937402.4</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>30937402.4</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-2241455.818365904</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>6558890</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>6558890.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>12.13</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>13.58</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>14.21</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>14.21</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>4662006.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>6815781.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>6815781.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>7509790.3</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>31054367.72</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>31054367.72</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-2474718.372283708</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>4662006</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>4662006.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>12.38</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>13.76</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>14.2</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>13.76</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>14.2</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>7354036.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>7220126.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>7220126.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>7690258.5</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>31465637.78</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>31465637.78</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-2516330.221727583</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>7354036</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>7354036.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>12.61</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>13.95</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>14.2</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>14.2</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>7510046.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>8012093.6</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>8012093.6</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>7946348.3</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>31843794.6</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>31843794.6</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-2774338.570157131</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>7510046</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>7510046.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>12.88</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>14.17</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>14.17</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>14.17</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>4649363.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>8009701.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>8009701.6</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>8175667.5</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>31841882.54</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>31841882.54</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-3060553.76183659</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>4649363</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>4649363.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>13.2</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>14.36</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>14.15</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>14.15</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>9903457.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>8303091.2</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>8303091.2</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>8508648.8</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>32120796.14</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>32120796.14</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-3053625.365598796</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>9903457</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>9903457.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>13.41</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>14.47</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>14.11</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>14.11</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>6683729.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>8203799.0</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>8203799</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>8613484.6</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>32261810.34</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>32261810.34</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-3497608.250773417</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>6683729</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>6683729.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>13.54</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>14.54</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>14.04</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>14.04</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>11313873.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>8160390.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>8160390.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>8745779.5</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>32301013.08</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>32301013.08</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-3661984.077780968</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>11313873</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>11313873.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>13.64</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>14.63</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>13.98</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>13.98</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>7498086.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>7880603.0</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>7880603</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>8787115.8</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>32213809.44</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>32213809.44</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-4262108.399299579</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>7498086</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>7498086.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>13.72</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>14.71</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>13.92</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>13.92</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>6116311.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>8341633.4</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>8341633.4</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>9420617.8</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>32160012.06</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>32160012.06</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-4558376.380065465</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>6116311</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>6116311.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>201.9</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>226.95</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>227.58</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>226.95</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>227.58</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>90663.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>114762.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>114762.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>123500.7</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>273993.44</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>273993.44</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-31215.27260816598</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>90663</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>90663.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>201.8</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>229.72</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>227.19</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>229.72</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>227.19</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>93169.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>125649.0</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>125649</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>130618.1</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>283082.9</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>283082.9</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-30570.17550505494</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>93169</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>93169.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>203.4</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>232.6</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>227.0</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>232.6</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>227</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>90567.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>147137.2</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>147137.2</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>171768.1</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>285167.84</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>285167.84</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-28825.31623257286</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>90567</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>90567.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>207.2</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>235.9</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>226.52</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>235.9</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>226.52</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>188545.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>150672.6</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>150672.6</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>224103.3</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>291936.48</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>291936.48</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-25024.39883500661</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>188545</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>188545.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>212.5</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>239.08</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>226.07</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>239.08</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>226.07</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>110870.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>128416.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>128416</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>221540.1</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>295295.0</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>295295</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-29198.43116580459</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>110870</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>110870.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>216.9</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>241.65</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>225.09</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>241.65</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>225.09</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>145094.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>132238.6</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>132238.6</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>233985.8</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>294618.16</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>294618.16</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-25796.21195388012</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>145094</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>145094.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>221.3</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>244.6</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>224.17</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>244.6</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>224.17</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>200610.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>135587.2</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>135587.2</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>249984.2</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>295031.98</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>295031.98</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-23681.46265277802</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>200610</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>200610.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>223.5</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>247.42</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>223.12</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>247.42</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>223.12</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>108244.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>196399.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>196399</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>271350.4</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>291675.48</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>291675.48</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-25762.76855646149</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>108244</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>108244.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>228.8</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>249.28</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>221.94</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>249.28</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>221.94</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>77262.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>297534.0</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>297534</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>296942.8</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>290061.26</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>290061.26</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-17919.60668470713</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>77262</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>77262.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>234.0</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>250.9</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>220.66</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>250.9</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>220.66</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>129983.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>314664.2</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>314664.2</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>313434.5</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>289641.36</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>289641.36</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-2755.603772032773</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>129983</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>129983.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>237.4</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>252.08</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>219.29</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>252.08</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>219.29</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>161837.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>335733.0</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>335733</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>325527.8</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>288207.54</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>288207.54</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>13356.99338078895</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>161837</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>161837.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>6.302</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>6.57</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>6.57</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>6.57</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>36325854.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>29986849.0</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>29986849</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>24630382.5</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>39591305.02</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>39591305.02</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-2561389.810234267</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>36325854</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>36325854.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>6.302</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>6.61</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>6.56</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>6.56</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>35567249.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>25618149.4</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>25618149.4</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>22763242.5</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>39659177.78</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>39659177.78</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-3718653.028287549</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>35567249</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>35567249.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>6.311999999999999</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>6.65</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>6.56</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>6.56</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>15411559.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>22322327.0</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>22322327</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>22977296.1</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>39401062.22</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>39401062.22</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-5157798.053067677</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>15411559</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>15411559.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>6.382</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>6.68</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>6.56</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>6.56</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>15720972.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>22981547.2</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>22981547.2</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>24041313.8</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>39535003.52</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>39535003.52</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-4869974.229429729</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>15720972</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>15720972.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>6.426</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>6.68</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>6.56</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>6.56</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>46908611.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>24130138.2</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>24130138.2</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>25727178.5</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>39552729.94</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>39552729.94</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-4318021.080324456</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>46908611</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>46908611.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>6.436</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>6.67</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>6.55</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>6.55</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>14482356.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>19273916.0</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>19273916</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>29106471.9</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>38877404.46</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>38877404.46</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-6716834.293019626</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>14482356</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>14482356.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>6.67</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>6.55</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>6.55</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>19088137.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>19908335.6</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>19908335.6</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>32251761.1</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>38987992.86</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>38987992.86</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-6429581.7649763</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>19088137</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>19088137.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,21 +27717,17 @@
           <t>6.529999999999999</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
+      <c r="AM64" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AO64" t="inlineStr">
         <is>
           <t>6.67</t>
         </is>
       </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>6.55</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>6.67</t>
-        </is>
-      </c>
       <c r="AP64" t="inlineStr">
         <is>
           <t>-101.03</t>
@@ -28144,20 +27768,16 @@
           <t>18707660.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>23632265.2</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>23632265.2</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>33228746.4</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>39121110.62</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>39121110.62</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-6283069.626165252</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>18707660</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>18707660.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>6.56</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>6.65</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>6.54</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>6.54</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>21463927.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>25101080.4</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>25101080.4</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>35104960.6</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>39133211.8</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>39133211.8</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-5808605.834072143</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>21463927</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>21463927.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>6.642</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>6.64</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>6.54</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>6.54</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>22627500.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>27324218.8</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>27324218.8</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>40925104.0</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>39344738.72</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>39344738.72</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-5218664.529865123</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>22627500</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>22627500.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>6.752</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>6.62</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>6.53</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>6.53</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>17654454.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>38939027.8</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>38939027.8</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>44983471.9</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>39497281.48</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>39497281.48</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-4314178.89778848</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>17654454</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>17654454.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>94.96000000000001</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>102.36</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>107.79</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>102.36</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>107.79</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>201371785.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>241585594.2</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>241585594.2</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>391104366.6</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>1504374242.12</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>1504374242.12</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-191018954.3335088</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>201371785</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>201371785.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>94.44</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>102.57</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>108.73</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>102.57</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>108.73</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>212282665.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>262256753.8</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>262256753.8</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>447757535.9</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>1569603789.94</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>1569603789.94</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-195652551.2250234</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>212282665</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>212282665.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>94.5</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>102.92</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>109.43</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>102.92</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>109.43</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>170614152.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>333387882.0</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>333387882</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>499097507.5</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>1622376544.82</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>1622376544.82</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-196453407.0977221</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>170614152</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>170614152.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>96.08000000000001</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>103.4</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>110.12</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>110.12</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>292246810.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>385454540.6</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>385454540.6</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>620641046.6</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>1711289280.24</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>1711289280.24</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-186116810.2695159</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>292246810</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>292246810.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>98.64</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>103.88</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>110.9</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>103.88</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>110.9</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>331412559.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>474610797.8</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>474610797.8</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>910559577.2</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>1764394296.32</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>1764394296.32</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-177735284.9338814</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>331412559</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>331412559.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>100.48</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>104.12</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>111.46</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>104.12</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>111.46</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>304727583.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>540623139.0</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>540623139</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>1033074216.6</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>1817944622.74</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>1817944622.74</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-163610318.8139077</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>304727583</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>304727583.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>102.84</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>104.76</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>111.96</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>104.76</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>111.96</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>567938306.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>633258318.0</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>633258318</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>1216731969.7</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>1859281366.72</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>1859281366.72</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-134729465.5420202</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>567938306</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>567938306.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>104.5</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>104.82</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>112.56</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>104.82</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>112.56</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>430947445.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>664807133.0</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>664807133</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>1501613925.2</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>1915776286.98</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>1915776286.98</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-116860485.9913944</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>430947445</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>430947445.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>105.3</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>104.76</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>113.06</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>104.76</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>113.06</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>738028096.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>855827552.6</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>855827552.6</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>1626976225.2</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>2024055315.18</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>2024055315.18</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-72482191.31223631</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>738028096</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>738028096.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>107.3</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>104.83</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>113.53</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>104.83</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>113.53</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>661474265.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>1346508356.6</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>1346508356.6</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>1613009835.6</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>2183695022.74</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>2183695022.74</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-39397476.11657333</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>661474265</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>661474265.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>107.8</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>104.7</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>113.99</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>113.99</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>767903478.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>1525525294.2</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>1525525294.2</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>1580511190.2</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>2239589271.02</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>2239589271.02</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>17475651.63139415</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>767903478</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>767903478.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
